--- a/astro-site/public/dl/guia-chocolateria-obrador/checklist-legal-licencias-y-cacao.xlsx
+++ b/astro-site/public/dl/guia-chocolateria-obrador/checklist-legal-licencias-y-cacao.xlsx
@@ -341,7 +341,7 @@
   <commentList>
     <comment ref="C8" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Ley 12/2012, de 26 de diciembre, de medidas urgentes de liberalización del comercio y de determinados servicios (BOE-A-2012-15595), texto consolidado · «Última modificación: 29... (Dos límites del propio texto: queda fuera lo que tenga impacto en el patrimonio histórico-artístico o en el uso priv... · https://www.boe.es/buscar/act.php?id=BOE-A-2012-15595</t>
+        <t>Verificado el 12-09-2026 · Ley 12/2012, de 26 de diciembre, de medidas urgentes de liberalización del comercio y de determinados servicios (BOE-A-2012-15595), texto consolidado · «Última modificación: 29... (Arts.) · https://www.boe.es/buscar/act.php?id=BOE-A-2012-15595</t>
       </text>
     </comment>
     <comment ref="C9" authorId="0" shapeId="0">
@@ -376,12 +376,12 @@
     </comment>
     <comment ref="C27" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Real Decreto 1021/2022, de 13 de diciembre, por el que se regulan determinados requisitos en materia de higiene de la producción y comercialización de los productos alimenticios en establecimientos de comercio al por menor (BOE-A-2022-21681), texto consolidado · «Última modificación: sin modifica... · https://www.boe.es/buscar/act.php?id=BOE-A-2022-21681</t>
+        <t>Verificado el 12-09-2026 · Real Decreto 1021/2022, de 13 de diciembre, por el que se regulan determinados requisitos en materia de higiene de la producción y comercialización de los productos alimenticios... (Lista estatal del obrador en vivienda (art. 13.8): las cinco letras) · https://www.boe.es/buscar/act.php?id=BOE-A-2022-21681</t>
       </text>
     </comment>
     <comment ref="C34" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Ley 7/2022, de 8 de abril, de residuos y suelos contaminados para una economía circular (BOE-A-2022-5809), texto consolidado · «Última modificación: 02 de abril de 2025» (Periodo de liquidación: trimestre natural, salvo IVA mensual (art. 82.1).) · https://www.boe.es/buscar/act.php?id=BOE-A-2022-5809</t>
+        <t>Verificado el 12-09-2026 · Ley 7/2022, de 8 de abril, de residuos y suelos contaminados para una economía circular (BOE-A-2022-5809), texto consolidado · «Última modificación: 02 de abril de 2025» (Arts.) · https://www.boe.es/buscar/act.php?id=BOE-A-2022-5809</t>
       </text>
     </comment>
     <comment ref="C35" authorId="0" shapeId="0">
@@ -436,7 +436,7 @@
     </comment>
     <comment ref="C51" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Ley 1/2004, de 21 de diciembre, de Horarios Comerciales (BOE-A-2004-21421), texto consolidado · «Última modificación: 17 de octubre de 2014» (Nuevo matiz que la lente no traía: el propio art. 5.1 da libertad plena también a los establecimientos situados «en zonas de gran afluenc...) · https://www.boe.es/buscar/act.php?id=BOE-A-2004-21421</t>
+        <t>Verificado el 12-09-2026 · Ley 1/2004, de 21 de diciembre, de Horarios Comerciales (BOE-A-2004-21421), texto consolidado · «Última modificación: 17 de octubre de 2014» (Nuevo matiz que la lente no traía: el propio art. 5.1 da libertad plena también a los establecimientos situados «en zonas de...) · https://www.boe.es/buscar/act.php?id=BOE-A-2004-21421</t>
       </text>
     </comment>
     <comment ref="C52" authorId="0" shapeId="0">
@@ -451,7 +451,7 @@
     </comment>
     <comment ref="C54" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Ley 1/2025, de 1 de abril, de prevención de las pérdidas y el desperdicio alimentario (BOE-A-2025-6597), texto consolidado · «Última modificación: sin modificaciones» (La lente decía «queda fuera del art. 6 … le siguen obligando el 6.2, el 6.3 y el 6.5», lo que se contradice a sí mismo y contradi... · https://www.boe.es/buscar/act.php?id=BOE-A-2025-6597</t>
+        <t>Verificado el 12-09-2026 · Ley 1/2025, de 1 de abril, de prevención de las pérdidas y el desperdicio alimentario (BOE-A-2025-6597), texto consolidado · «Última modificación: sin modificaciones» (La lente decía «queda fuera del art. 6 … le siguen obligando el 6.2, el 6.3 y el 6.5», lo que se contradice a sí...) · https://www.boe.es/buscar/act.php?id=BOE-A-2025-6597</t>
       </text>
     </comment>
     <comment ref="D69" authorId="0" shapeId="0">
@@ -486,7 +486,7 @@
     </comment>
     <comment ref="B78" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Lo que sigue abierto es el TIPO: el art. 91 no nombra los talleres, así que por la regla general del art. 90.Uno sería el 21 %, salvo que...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
+        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Lo que sigue abierto es el TIPO: el art. 91 no nombra los talleres, así que por la regla general del art. 90.Uno ser...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
       </text>
     </comment>
     <comment ref="C82" authorId="0" shapeId="0">
@@ -616,7 +616,7 @@
     </comment>
     <comment ref="B7" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Real Decreto 1021/2022, de 13 de diciembre, por el que se regulan determinados requisitos en materia de higiene de la producción y comercialización de los productos alimenticios en establecimientos de comercio al por menor (BOE-A-2022-21681), texto consolidado · «Última modificación: sin modifica... · https://www.boe.es/buscar/act.php?id=BOE-A-2022-21681</t>
+        <t>Verificado el 12-09-2026 · Real Decreto 1021/2022, de 13 de diciembre, por el que se regulan determinados requisitos en materia de higiene de la producción y comercialización de los productos alimenticios... (Lista estatal del obrador en vivienda (art. 13.8): las cinco letras) · https://www.boe.es/buscar/act.php?id=BOE-A-2022-21681</t>
       </text>
     </comment>
     <comment ref="B8" authorId="0" shapeId="0">
@@ -631,7 +631,7 @@
     </comment>
     <comment ref="B17" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Real Decreto 1021/2022, de 13 de diciembre, por el que se regulan determinados requisitos en materia de higiene de la producción y comercialización de los productos alimenticios en establecimientos de comercio al por menor (BOE-A-2022-21681), texto consolidado · «Última modificación: sin modifica... · https://www.boe.es/buscar/act.php?id=BOE-A-2022-21681</t>
+        <t>Verificado el 12-09-2026 · Real Decreto 1021/2022, de 13 de diciembre, por el que se regulan determinados requisitos en materia de higiene de la producción y comercialización de los productos alimenticios... (Lista estatal del obrador en vivienda (art. 13.8): las cinco letras) · https://www.boe.es/buscar/act.php?id=BOE-A-2022-21681</t>
       </text>
     </comment>
     <comment ref="B20" authorId="0" shapeId="0">
@@ -656,7 +656,7 @@
   <commentList>
     <comment ref="B7" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Reglamento (UE) 2023/915 de la Comisión, de 25 de abril de 2023, relativo a los límites máximos de determinados contaminantes en los alimentos · texto consolidado CELEX:02023R09... (La nota (14) del Anexo I remite SOLO a los puntos 2, 3 y 4 de la parte A del Anexo I de la Directiva 2000/36/CE: ca... · https://eur-lex.europa.eu/legal-content/ES/TXT/HTML/?uri=CELEX:02023R0915-20250101</t>
+        <t>Verificado el 12-09-2026 · Reglamento (UE) 2023/915 de la Comisión, de 25 de abril de 2023, relativo a los límites máximos de determinados contaminantes en los alimentos · texto consolidado CELEX:02023R09... (La nota (14) del Anexo I remite SOLO a los puntos 2, 3 y 4 de la parte A del Anexo I de la Direct...) · https://eur-lex.europa.eu/legal-content/ES/TXT/HTML/?uri=CELEX:02023R0915-20250101</t>
       </text>
     </comment>
     <comment ref="B9" authorId="0" shapeId="0">
@@ -676,7 +676,7 @@
     </comment>
     <comment ref="B26" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Reglamento (UE) 2023/915 de la Comisión, de 25 de abril de 2023, relativo a los límites máximos de determinados contaminantes en los alimentos · texto consolidado CELEX:02023R09... (2.1, 2.2, 3.1, 3.2 y 4 («Los alimentos que contengan contaminantes recogidos en el anexo I no serán destoxificados... · https://eur-lex.europa.eu/legal-content/ES/TXT/HTML/?uri=CELEX:02023R0915-20250101</t>
+        <t>Verificado el 12-09-2026 · Reglamento (UE) 2023/915 de la Comisión, de 25 de abril de 2023, relativo a los límites máximos de determinados contaminantes en los alimentos · texto consolidado CELEX:02023R09... (Arts.) · https://eur-lex.europa.eu/legal-content/ES/TXT/HTML/?uri=CELEX:02023R0915-20250101</t>
       </text>
     </comment>
     <comment ref="B29" authorId="0" shapeId="0">
@@ -721,7 +721,7 @@
     </comment>
     <comment ref="B15" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Reglamento (UE) 2023/1115 del Parlamento Europeo y del Consejo, de 31 de mayo de 2023 (EUDR) · texto consolidado CELEX:02023R1115-20251226 (versión 26-12-2025, 002.001) (El art. 38.3 difiere la aplicación solo para los «operadores» que sean persona física, microempresa o pequeña empresa y estuvie... · https://eur-lex.europa.eu/legal-content/ES/TXT/HTML/?uri=CELEX:02023R1115-20251226</t>
+        <t>Verificado el 12-09-2026 · Reglamento (UE) 2023/1115 del Parlamento Europeo y del Consejo, de 31 de mayo de 2023 (EUDR) · texto consolidado CELEX:02023R1115-20251226 (versión 26-12-2025, 002.001) (Los arts.) · https://eur-lex.europa.eu/legal-content/ES/TXT/HTML/?uri=CELEX:02023R1115-20251226</t>
       </text>
     </comment>
     <comment ref="B18" authorId="0" shapeId="0">
@@ -741,7 +741,7 @@
     </comment>
     <comment ref="B21" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Reglamento (UE) 2023/1115 del Parlamento Europeo y del Consejo, de 31 de mayo de 2023 (EUDR) · texto consolidado CELEX:02023R1115-20251226 (versión 26-12-2025, 002.001) (El art. 38.3 difiere la aplicación solo para los «operadores» que sean persona física, microempresa o pequeña empresa y estuvie... · https://eur-lex.europa.eu/legal-content/ES/TXT/HTML/?uri=CELEX:02023R1115-20251226</t>
+        <t>Verificado el 12-09-2026 · Reglamento (UE) 2023/1115 del Parlamento Europeo y del Consejo, de 31 de mayo de 2023 (EUDR) · texto consolidado CELEX:02023R1115-20251226 (versión 26-12-2025, 002.001) (Los arts.) · https://eur-lex.europa.eu/legal-content/ES/TXT/HTML/?uri=CELEX:02023R1115-20251226</t>
       </text>
     </comment>
     <comment ref="B25" authorId="0" shapeId="0">
@@ -751,7 +751,7 @@
     </comment>
     <comment ref="C25" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Reglamento (UE) 2023/1115 del Parlamento Europeo y del Consejo, de 31 de mayo de 2023 (EUDR) · texto consolidado CELEX:02023R1115-20251226 (versión 26-12-2025, 002.001) (El art. 3 exige tres condiciones acumulativas: libres de deforestación, producidos conforme a la legislación del país de produc... · https://eur-lex.europa.eu/legal-content/ES/TXT/HTML/?uri=CELEX:02023R1115-20251226</t>
+        <t>Verificado el 12-09-2026 · Reglamento (UE) 2023/1115 del Parlamento Europeo y del Consejo, de 31 de mayo de 2023 (EUDR) · texto consolidado CELEX:02023R1115-20251226 (versión 26-12-2025, 002.001) (Arts.) · https://eur-lex.europa.eu/legal-content/ES/TXT/HTML/?uri=CELEX:02023R1115-20251226</t>
       </text>
     </comment>
   </commentList>
@@ -781,7 +781,7 @@
   <commentList>
     <comment ref="B12" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Ley 12/2012, de 26 de diciembre, de medidas urgentes de liberalización del comercio y de determinados servicios (BOE-A-2012-15595), texto consolidado · «Última modificación: 29... (Dos límites del propio texto: queda fuera lo que tenga impacto en el patrimonio histórico-artístico o en el uso priv... · https://www.boe.es/buscar/act.php?id=BOE-A-2012-15595</t>
+        <t>Verificado el 12-09-2026 · Ley 12/2012, de 26 de diciembre, de medidas urgentes de liberalización del comercio y de determinados servicios (BOE-A-2012-15595), texto consolidado · «Última modificación: 29... (Arts.) · https://www.boe.es/buscar/act.php?id=BOE-A-2012-15595</t>
       </text>
     </comment>
   </commentList>
